--- a/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Joanne et papa sont dans la cour. Papa trace un petit cercle. Papa dit : voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.</t>
+          <t>Joanne et papa sont dans la cour. Papa trace un petit cercle. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Joanne et papa sont dans la cour. Papa trace un petit cercle.
+papa|Voici l'espace du jeu. On se passe le ballon. Chacun a un tour.
+narrateur|Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Joanne joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Joanne a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Joanne boit une gorgée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Joanne joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Joanne a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Papa range le ballon. Joanne boit une gorgée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joanne se passe le ballon</t>
+          <t>Mila se passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une feuille tourne au-dessus de la cour. Mila et papa se passent le ballon dans l'espace du jeu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Joanne et papa sont dans la cour. Papa trace un petit cercle. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.</t>
+          <t>Une feuille sèche tourne au-dessus de la cour. Elle va, elle vient, tout lentement. L'ombre du platane est fraîche. Les dalles sentent encore le soleil. Un lézard gris file le long du mur. Mila, tu as vu la feuille ? Oui, papa. Elle tourne. En ce moment, Mila entre dans la cour. Ses sandales tapent un peu. Papa trace un petit cercle au sol. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Mila touche le ballon. Il est lisse et un peu chaud. Il est chaud, papa. Oui. Il a pris le soleil. Mila passe le ballon à papa. Papa l'attrape. Il le rend. Mila attend son tour. Ses pieds restent dans l'espace du jeu. Tu attends. C'est bien. Puis elle passe encore. Le ballon reste près, dans le cercle. Tu restes dans l'espace. Le ballon reste près. Je reste ici. Oui. C'est l'espace du jeu. La feuille tourne encore. Mila lève les yeux, puis attend. C'est ton tour, Mila. Elle passe le ballon. Papa l'attrape contre le ventre. Bravo. Tu as passé. Ils se passent le ballon encore. Mila attend. Puis c'est son tour. Chacun a un tour. Tu as bien joué. Un oiseau saute dans l'ombre. Encore un passage ? Oui. On reste dans l'espace du jeu. Mila attend. Papa passe. Mila passe. Le ballon est doux. Bien joué, Mila. Le lézard s'est arrêté sur une pierre chaude. Il se repose. Et toi, tu attends ton tour. Mila attend. Puis elle passe. Tu as fait du bon travail. La feuille tombe près du cercle. Mila la regarde, puis elle attend. C'est encore ton tour. Elle passe le ballon tout doucement. J'ai attrapé. Bravo. L'ombre sent un peu la poussière. Le platane est grand. Oui. Et toi, tu restes dans l'espace. Mila reste dans l'espace du jeu. Papa passe. Mila attend, puis elle passe. Chacun a un tour. C'est bien. Un oiseau picore près du mur. Il cherche. Et nous, on se passe le ballon. Mila rit. Le ballon est chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Joanne et papa sont dans la cour. Papa trace un petit cercle.
-papa|Voici l'espace du jeu. On se passe le ballon. Chacun a un tour.
-narrateur|Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une feuille sèche tourne au-dessus de la cour.
+narrateur|Elle va, elle vient, tout lentement.
+narrateur|L'ombre du platane est fraîche.
+narrateur|Les dalles sentent encore le soleil.
+narrateur|Un lézard gris file le long du mur.
+papa|Mila, tu as vu la feuille ?
+enfant-f|Oui, papa. Elle tourne.
+narrateur|En ce moment, Mila entre dans la cour.
+narrateur|Ses sandales tapent un peu.
+narrateur|Papa trace un petit cercle au sol.
+papa|Voici l'espace du jeu.
+papa|On se passe le ballon.
+papa|Chacun a un tour.
+narrateur|Mila touche le ballon.
+narrateur|Il est lisse et un peu chaud.
+enfant-f|Il est chaud, papa.
+papa|Oui. Il a pris le soleil.
+narrateur|Mila passe le ballon à papa.
+narrateur|Papa l'attrape. Il le rend.
+narrateur|Mila attend son tour.
+narrateur|Ses pieds restent dans l'espace du jeu.
+papa|Tu attends. C'est bien.
+narrateur|Puis elle passe encore.
+narrateur|Le ballon reste près, dans le cercle.
+papa|Tu restes dans l'espace. Le ballon reste près.
+enfant-f|Je reste ici.
+papa|Oui. C'est l'espace du jeu.
+narrateur|La feuille tourne encore.
+narrateur|Mila lève les yeux, puis attend.
+papa|C'est ton tour, Mila.
+narrateur|Elle passe le ballon.
+narrateur|Papa l'attrape contre le ventre.
+papa|Bravo. Tu as passé.
+narrateur|Ils se passent le ballon encore.
+narrateur|Mila attend. Puis c'est son tour.
+papa|Chacun a un tour. Tu as bien joué.
+narrateur|Un oiseau saute dans l'ombre.
+enfant-f|Encore un passage ?
+papa|Oui. On reste dans l'espace du jeu.
+narrateur|Mila attend. Papa passe.
+narrateur|Mila passe. Le ballon est doux.
+papa|Bien joué, Mila.
+narrateur|Le lézard s'est arrêté sur une pierre chaude.
+enfant-f|Il se repose.
+papa|Et toi, tu attends ton tour.
+narrateur|Mila attend. Puis elle passe.
+papa|Tu as fait du bon travail.
+narrateur|La feuille tombe près du cercle.
+narrateur|Mila la regarde, puis elle attend.
+papa|C'est encore ton tour.
+narrateur|Elle passe le ballon tout doucement.
+papa|J'ai attrapé. Bravo.
+narrateur|L'ombre sent un peu la poussière.
+enfant-f|Le platane est grand.
+papa|Oui. Et toi, tu restes dans l'espace.
+narrateur|Mila reste dans l'espace du jeu.
+narrateur|Papa passe. Mila attend, puis elle passe.
+papa|Chacun a un tour. C'est bien.
+narrateur|Un oiseau picore près du mur.
+enfant-f|Il cherche.
+papa|Et nous, on se passe le ballon.
+narrateur|Mila rit. Le ballon est chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Joanne joue au ballon. Que fait-elle ?</t>
+          <t>Mila joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,10 +1568,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Joanne joue au ballon. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila joue au ballon.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Joanne a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
+          <t>Mila a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es restée dans l'espace. Chacun a un tour. Oui. Bravo, Mila. L'ombre du platane a bougé un peu. La feuille sèche est près du cercle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1740,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Joanne a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a passé le ballon.
+narrateur|Elle a attendu son tour.
+narrateur|Dans l'espace du jeu.
+papa|Tu as passé. Tu as attendu.
+papa|Tu es restée dans l'espace.
+enfant-f|Chacun a un tour.
+papa|Oui. Bravo, Mila.
+narrateur|L'ombre du platane a bougé un peu.
+narrateur|La feuille sèche est près du cercle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Joanne boit une gorgée.</t>
+          <t>Papa range le ballon. Tu veux une gorgée d'eau ? Oui, papa. Mila boit une gorgée. L'eau est fraîche. On rentre. La cour est calme. Les sandales tapent encore. Ils rentrent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1911,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Joanne boit une gorgée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon.
+papa|Tu veux une gorgée d'eau ?
+enfant-f|Oui, papa.
+narrateur|Mila boit une gorgée.
+narrateur|L'eau est fraîche.
+papa|On rentre. La cour est calme.
+narrateur|Les sandales tapent encore.
+narrateur|Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon est rangé. Mila a passé. Elle a attendu. Bravo, Mila. Tu as bien joué. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,10 +2085,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon est rangé.
+narrateur|Mila a passé. Elle a attendu.
+papa|Bravo, Mila. Tu as bien joué.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille sèche tourne au-dessus de la cour. Elle va, elle vient, tout lentement. L'ombre du platane est fraîche. Les dalles sentent encore le soleil. Un lézard gris file le long du mur. Mila, tu as vu la feuille ? Oui, papa. Elle tourne. En ce moment, Mila entre dans la cour. Ses sandales tapent un peu. Papa trace un petit cercle au sol. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Mila touche le ballon. Il est lisse et un peu chaud. Il est chaud, papa. Oui. Il a pris le soleil. Mila passe le ballon à papa. Papa l'attrape. Il le rend. Mila attend son tour. Ses pieds restent dans l'espace du jeu. Tu attends. C'est bien. Puis elle passe encore. Le ballon reste près, dans le cercle. Tu restes dans l'espace. Le ballon reste près. Je reste ici. Oui. C'est l'espace du jeu. La feuille tourne encore. Mila lève les yeux, puis attend. C'est ton tour, Mila. Elle passe le ballon. Papa l'attrape contre le ventre. Bravo. Tu as passé. Ils se passent le ballon encore. Mila attend. Puis c'est son tour. Chacun a un tour. Tu as bien joué. Un oiseau saute dans l'ombre. Encore un passage ? Oui. On reste dans l'espace du jeu. Mila attend. Papa passe. Mila passe. Le ballon est doux. Bien joué, Mila. Le lézard s'est arrêté sur une pierre chaude. Il se repose. Et toi, tu attends ton tour. Mila attend. Puis elle passe. Tu as fait du bon travail. La feuille tombe près du cercle. Mila la regarde, puis elle attend. C'est encore ton tour. Elle passe le ballon tout doucement. J'ai attrapé. Bravo. L'ombre sent un peu la poussière. Le platane est grand. Oui. Et toi, tu restes dans l'espace. Mila reste dans l'espace du jeu. Papa passe. Mila attend, puis elle passe. Chacun a un tour. C'est bien. Un oiseau picore près du mur. Il cherche. Et nous, on se passe le ballon. Mila rit. Le ballon est chaud.</t>
+          <t>Une feuille sèche tourne au-dessus de la cour. Elle va, elle vient, tout lentement. L'ombre du platane est fraîche. Les dalles sentent encore le soleil. Un lézard gris file le long du mur. Mila, tu as vu la feuille ? Oui, papa. Elle tourne. En ce moment, Mila entre dans la cour. Ses sandales tapent un peu. Papa trace un petit cercle au sol. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Mila touche le ballon. Il est lisse et un peu chaud. Il est chaud, papa. Oui. Il a pris le soleil. Mila passe le ballon à papa. Papa l'attrape. Il le rend. Mila attend son tour. Ses pieds restent dans l'espace du jeu. Tu attends. C'est bien. Puis elle passe encore. Le ballon reste près, dans le cercle. Tu restes dans l'espace. Le ballon reste près. Je reste ici. Oui. C'est l'espace du jeu. La feuille tourne encore. Mila lève les yeux, puis attend. C'est ton tour, Mila. Elle passe le ballon. Papa l'attrape contre le ventre. Bravo. Tu as passé. Ils se passent le ballon encore. Mila attend. Puis c'est son tour. Chacun a un tour. Tu as bien joué. Un oiseau saute dans l'ombre. Encore un passage ? Oui. On reste dans l'espace du jeu. Mila attend. Papa passe. Mila passe. Le ballon est doux. Bien joué, Mila. Le lézard s'est arrêté sur une pierre chaude. Il se repose. Et toi, tu attends ton tour. Mila attend. Puis elle passe. La feuille tombe près du cercle. Mila la regarde, puis elle attend. C'est encore ton tour. Elle passe le ballon tout doucement. J'ai attrapé. Bravo. L'ombre sent un peu la poussière. Le platane est grand. Oui. Et toi, tu restes dans l'espace. Mila reste dans l'espace du jeu. Papa passe. Mila attend, puis elle passe. Chacun a un tour. C'est bien. Un oiseau picore près du mur. Il cherche. Et nous, on se passe le ballon. Mila rit. Le ballon est chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Joanne et papa sont dans la cour. Papa trace un petit cercle. Papa dit : voici l'espace du jeu. On se passe le ballon. Chacun a un &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Joanne touche le ballon. Elle passe le ballon à papa. Papa le rend. Joanne attend son tour. Puis elle passe encore. Les pieds restent dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille sèche tourne au-dessus de la cour. Elle va, elle vient, tout lentement. L'ombre du platane est fraîche. Les dalles sentent encore le soleil. Un lézard gris file le long du mur. Mila, tu as vu la feuille ? Oui, papa. Elle tourne. En ce moment, Mila entre dans la cour. Ses sandales tapent un peu. Papa trace un petit cercle au sol. Voici l'espace du jeu. On se passe le ballon. Chacun a un tour. Mila touche le ballon. Il est lisse et un peu chaud. Il est chaud, papa. Oui. Il a pris le soleil. Mila passe le ballon à papa. Papa l'attrape. Il le rend. Mila attend son tour. Ses pieds restent dans l'espace du jeu. Tu attends. C'est bien. Puis elle passe encore. Le ballon reste près, dans le cercle. Tu restes dans l'espace. Le ballon reste près. Je reste ici. Oui. C'est l'espace du jeu. La feuille tourne encore. Mila lève les yeux, puis attend. C'est ton tour, Mila. Elle passe le ballon. Papa l'attrape contre le ventre. Bravo. Tu as passé. Ils se passent le ballon encore. Mila attend. Puis c'est son tour. Chacun a un tour. Tu as bien joué. Un oiseau saute dans l'ombre. Encore un passage ? Oui. On reste dans l'espace du jeu. Mila attend. Papa passe. Mila passe. Le ballon est doux. Bien joué, Mila. Le lézard s'est arrêté sur une pierre chaude. Il se repose. Et toi, tu attends ton tour. Mila attend. Puis elle passe. La feuille tombe près du cercle. Mila la regarde, puis elle attend. C'est encore ton tour. Elle passe le ballon tout doucement. J'ai attrapé. Bravo. L'ombre sent un peu la poussière. Le platane est grand. Oui. Et toi, tu restes dans l'espace. Mila reste dans l'espace du jeu. Papa passe. Mila attend, puis elle passe. Chacun a un tour. C'est bien. Un oiseau picore près du mur. Il cherche. Et nous, on se passe le ballon. Mila rit. Le ballon est chaud.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1370,7 +1370,6 @@
 enfant-f|Il se repose.
 papa|Et toi, tu attends ton tour.
 narrateur|Mila attend. Puis elle passe.
-papa|Tu as fait du bon travail.
 narrateur|La feuille tombe près du cercle.
 narrateur|Mila la regarde, puis elle attend.
 papa|C'est encore ton tour.
@@ -1417,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Joanne joue au ballon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila joue au ballon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Joanne a passé le ballon. Elle a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a passé le ballon. Elle a attendu son tour. Dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es restée dans l'espace. Chacun a un tour. Oui. Bravo, Mila. L'ombre du platane a bougé un peu. La feuille sèche est près du cercle.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1780,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le ballon. Joanne boit une gorgée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon. Tu veux une gorgée d'eau ? Oui, papa. Mila boit une gorgée. L'eau est fraîche. On rentre. La cour est calme. Les sandales tapent encore. Ils rentrent.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon est rangé. Mila a passé. Elle a attendu. Bravo, Mila. Tu as bien joué. L'histoire est finie.</t>
+          <t>Le ballon est rangé. Mila a passé. Elle a attendu. Bravo, Mila. Tu as bien joué.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon est rangé. Mila a passé. Elle a attendu. Bravo, Mila. Tu as bien joué.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2087,8 +2086,7 @@
         <is>
           <t>narrateur|Le ballon est rangé.
 narrateur|Mila a passé. Elle a attendu.
-papa|Bravo, Mila. Tu as bien joué.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Mila. Tu as bien joué.</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2152,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Joanne, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
